--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D37A170-0CAA-4DDF-9B00-48E260830A9F}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E638E3-04A4-4A72-8E18-A16296BB53F1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -223,11 +223,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="&quot;　請求金額 ： \ &quot;#,##0&quot;　&quot;;&quot;　請求金額 ： \ &quot;\-#,##0&quot;　&quot;"/>
     <numFmt numFmtId="178" formatCode="&quot;　&quot;yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="183" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -603,7 +602,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -757,28 +756,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1197,6 +1189,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
+      <c r="D17" s="47"/>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1344,18 +1337,18 @@
       <c r="E32" s="25"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="50"/>
+      <c r="A33" s="48"/>
       <c r="B33" s="14"/>
       <c r="C33" s="34"/>
       <c r="D33" s="35"/>
       <c r="E33" s="25"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="50"/>
-      <c r="C34" s="45" t="s">
+      <c r="A34" s="48"/>
+      <c r="C34" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="46"/>
+      <c r="D34" s="27"/>
       <c r="E34" s="36"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1363,8 +1356,8 @@
         <v>8</v>
       </c>
       <c r="B35" s="23"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="48"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="37"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1452,8 +1445,8 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="43"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="46"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
@@ -1529,6 +1522,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
+      <c r="D17" s="47"/>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1676,14 +1670,14 @@
       <c r="E32" s="25"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="50"/>
+      <c r="A33" s="48"/>
       <c r="B33" s="14"/>
       <c r="C33" s="34"/>
       <c r="D33" s="35"/>
       <c r="E33" s="25"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="50"/>
+      <c r="A34" s="48"/>
       <c r="C34" s="26" t="s">
         <v>14</v>
       </c>
@@ -1716,11 +1710,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:E35"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="C36:D37"/>
     <mergeCell ref="E36:E37"/>
@@ -1731,6 +1720,11 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:E11"/>
     <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:E35"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E17:E31">

--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E638E3-04A4-4A72-8E18-A16296BB53F1}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC99F8D8-25FB-4C5B-88FE-27BBFC8DDD71}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -602,7 +602,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -688,6 +688,9 @@
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -728,6 +731,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -744,10 +751,7 @@
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -762,15 +766,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1088,65 +1091,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
       <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="43"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="43"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
+      <c r="A9" s="44"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="43"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
+      <c r="A10" s="44"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1189,7 +1192,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="47"/>
+      <c r="D17" s="24"/>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1210,170 +1213,134 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10"/>
       <c r="D20" s="11"/>
-      <c r="E20" s="17" t="str">
-        <f t="shared" ref="E20:E31" si="0">IF(COUNTBLANK(B20:D20)=3,"",TRUNC(B20*D20))</f>
-        <v/>
-      </c>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="10"/>
       <c r="D21" s="11"/>
-      <c r="E21" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
-      <c r="E22" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="10"/>
       <c r="D24" s="11"/>
-      <c r="E24" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
       <c r="C27" s="10"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="10"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="10"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B32" s="16"/>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="48"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="25"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="48"/>
-      <c r="C34" s="26" t="s">
+      <c r="A34" s="43"/>
+      <c r="C34" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="36"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="23"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="37"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="41"/>
-      <c r="C36" s="30" t="s">
+      <c r="A36" s="50"/>
+      <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="36"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="42"/>
+      <c r="A37" s="49"/>
       <c r="B37" s="21"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="38"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1421,65 +1388,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
       <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="47"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="43"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
+      <c r="A9" s="44"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="43"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
+      <c r="A10" s="44"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1522,7 +1489,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="47"/>
+      <c r="D17" s="24"/>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1543,170 +1510,134 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10"/>
       <c r="D20" s="11"/>
-      <c r="E20" s="17" t="str">
-        <f t="shared" ref="E20:E31" si="0">IF(COUNTBLANK(B20:D20)=3,"",TRUNC(B20*D20))</f>
-        <v/>
-      </c>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="10"/>
       <c r="D21" s="11"/>
-      <c r="E21" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
-      <c r="E22" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="10"/>
       <c r="D24" s="11"/>
-      <c r="E24" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
       <c r="C27" s="10"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="10"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="10"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B32" s="16"/>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="48"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="25"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="48"/>
-      <c r="C34" s="26" t="s">
+      <c r="A34" s="43"/>
+      <c r="C34" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="36"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="23"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="37"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="41"/>
-      <c r="C36" s="30" t="s">
+      <c r="A36" s="48"/>
+      <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="36"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="42"/>
+      <c r="A37" s="49"/>
       <c r="B37" s="21"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="38"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC99F8D8-25FB-4C5B-88FE-27BBFC8DDD71}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7829F932-4FAA-46D2-919C-F968C0758B68}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -602,7 +602,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -766,14 +766,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1127,29 +1131,29 @@
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="44"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="44"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1328,7 +1332,7 @@
       <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="50"/>
+      <c r="A36" s="51"/>
       <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
@@ -1336,7 +1340,7 @@
       <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="49"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="21"/>
       <c r="C37" s="33"/>
       <c r="D37" s="34"/>
@@ -1424,29 +1428,29 @@
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="44"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="44"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1625,7 +1629,7 @@
       <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="48"/>
+      <c r="A36" s="49"/>
       <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
@@ -1633,7 +1637,7 @@
       <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="49"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="21"/>
       <c r="C37" s="33"/>
       <c r="D37" s="34"/>

--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7829F932-4FAA-46D2-919C-F968C0758B68}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBA89AD2-12B5-459C-BBAF-89DB242CC7FE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -602,7 +602,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -751,33 +751,36 @@
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1119,8 +1122,8 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="44"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="47"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
@@ -1131,29 +1134,29 @@
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="44"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="44"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1207,6 +1210,7 @@
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="52"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1308,14 +1312,14 @@
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="43"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="14"/>
       <c r="C33" s="35"/>
       <c r="D33" s="36"/>
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="43"/>
+      <c r="A34" s="44"/>
       <c r="C34" s="27" t="s">
         <v>13</v>
       </c>
@@ -1332,7 +1336,7 @@
       <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="51"/>
+      <c r="A36" s="45"/>
       <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
@@ -1340,7 +1344,7 @@
       <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="50"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="21"/>
       <c r="C37" s="33"/>
       <c r="D37" s="34"/>
@@ -1416,8 +1420,8 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="47"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
@@ -1428,29 +1432,29 @@
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="44"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="44"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1504,6 +1508,7 @@
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="52"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1605,14 +1610,14 @@
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="43"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="14"/>
       <c r="C33" s="35"/>
       <c r="D33" s="36"/>
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="43"/>
+      <c r="A34" s="44"/>
       <c r="C34" s="27" t="s">
         <v>14</v>
       </c>
@@ -1637,7 +1642,7 @@
       <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="50"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="21"/>
       <c r="C37" s="33"/>
       <c r="D37" s="34"/>

--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBA89AD2-12B5-459C-BBAF-89DB242CC7FE}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA4D098C-669A-4BE0-A8BC-6737F88EEEB9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -602,7 +602,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -691,6 +691,9 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -767,9 +770,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -778,9 +778,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1098,65 +1095,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
       <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="47"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
+      <c r="A9" s="48"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
+      <c r="A10" s="48"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1210,7 +1207,7 @@
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="52"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1305,50 +1302,50 @@
         <v>7</v>
       </c>
       <c r="B32" s="16"/>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="26"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="44"/>
+      <c r="A33" s="45"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="26"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="44"/>
-      <c r="C34" s="27" t="s">
+      <c r="A34" s="45"/>
+      <c r="C34" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="38"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="39"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="23"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="39"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="45"/>
-      <c r="C36" s="31" t="s">
+      <c r="A36" s="46"/>
+      <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="38"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="46"/>
+      <c r="A37" s="47"/>
       <c r="B37" s="21"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="40"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1396,27 +1393,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
       <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
@@ -1427,34 +1424,34 @@
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
+      <c r="A9" s="48"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
+      <c r="A10" s="48"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1508,7 +1505,7 @@
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="52"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1603,50 +1600,50 @@
         <v>7</v>
       </c>
       <c r="B32" s="16"/>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="26"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="44"/>
+      <c r="A33" s="45"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="26"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="44"/>
-      <c r="C34" s="27" t="s">
+      <c r="A34" s="45"/>
+      <c r="C34" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="38"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="39"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="23"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="39"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="49"/>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="38"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="46"/>
+      <c r="A37" s="47"/>
       <c r="B37" s="21"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="40"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA4D098C-669A-4BE0-A8BC-6737F88EEEB9}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7783806-FAD3-49EA-853D-F56183DB428C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -223,10 +223,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="&quot;　請求金額 ： \ &quot;#,##0&quot;　&quot;;&quot;　請求金額 ： \ &quot;\-#,##0&quot;　&quot;"/>
     <numFmt numFmtId="178" formatCode="&quot;　&quot;yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="179" formatCode="[&lt;=999]000;[&lt;=9999]000\-00;000\-0000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -751,10 +752,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -770,14 +767,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1119,41 +1120,41 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="48"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="48"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1309,14 +1310,14 @@
       <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="45"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="14"/>
       <c r="C33" s="36"/>
       <c r="D33" s="37"/>
       <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="45"/>
+      <c r="A34" s="44"/>
       <c r="C34" s="28" t="s">
         <v>13</v>
       </c>
@@ -1333,7 +1334,7 @@
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="46"/>
+      <c r="A36" s="45"/>
       <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
@@ -1341,7 +1342,7 @@
       <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="47"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="21"/>
       <c r="C37" s="34"/>
       <c r="D37" s="35"/>
@@ -1417,41 +1418,41 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="48"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="48"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1607,14 +1608,14 @@
       <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="45"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="14"/>
       <c r="C33" s="36"/>
       <c r="D33" s="37"/>
       <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="45"/>
+      <c r="A34" s="44"/>
       <c r="C34" s="28" t="s">
         <v>14</v>
       </c>
@@ -1631,7 +1632,7 @@
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="49"/>
+      <c r="A36" s="50"/>
       <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
@@ -1639,7 +1640,7 @@
       <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="47"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="21"/>
       <c r="C37" s="34"/>
       <c r="D37" s="35"/>

--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7783806-FAD3-49EA-853D-F56183DB428C}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE1299E1-52C5-4370-AAC0-D5024F2AEA96}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -751,6 +751,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -758,12 +762,6 @@
     <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -773,12 +771,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1120,41 +1120,41 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
+      <c r="A9" s="46"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
+      <c r="A10" s="46"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1310,14 +1310,14 @@
       <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="44"/>
+      <c r="A33" s="45"/>
       <c r="B33" s="14"/>
       <c r="C33" s="36"/>
       <c r="D33" s="37"/>
       <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="44"/>
+      <c r="A34" s="45"/>
       <c r="C34" s="28" t="s">
         <v>13</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="45"/>
+      <c r="A36" s="49"/>
       <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
@@ -1342,7 +1342,7 @@
       <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="46"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="21"/>
       <c r="C37" s="34"/>
       <c r="D37" s="35"/>
@@ -1418,41 +1418,41 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
+      <c r="A9" s="46"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
+      <c r="A10" s="46"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="19"/>
@@ -1608,14 +1608,14 @@
       <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="44"/>
+      <c r="A33" s="45"/>
       <c r="B33" s="14"/>
       <c r="C33" s="36"/>
       <c r="D33" s="37"/>
       <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="44"/>
+      <c r="A34" s="45"/>
       <c r="C34" s="28" t="s">
         <v>14</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="50"/>
+      <c r="A36" s="51"/>
       <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
@@ -1640,7 +1640,7 @@
       <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="46"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="21"/>
       <c r="C37" s="34"/>
       <c r="D37" s="35"/>

--- a/public/invoice-default-template.xlsx
+++ b/public/invoice-default-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE1299E1-52C5-4370-AAC0-D5024F2AEA96}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C776EA5-927C-450C-BF24-0904ABA71DDE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -762,8 +762,11 @@
     <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -771,14 +774,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1120,8 +1120,8 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
@@ -1137,13 +1137,13 @@
       <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="46"/>
+      <c r="A9" s="51"/>
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="46"/>
+      <c r="A10" s="51"/>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
       <c r="E10" s="44"/>
@@ -1334,7 +1334,7 @@
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="49"/>
+      <c r="A36" s="46"/>
       <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
@@ -1342,7 +1342,7 @@
       <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="50"/>
+      <c r="A37" s="47"/>
       <c r="B37" s="21"/>
       <c r="C37" s="34"/>
       <c r="D37" s="35"/>
@@ -1418,8 +1418,8 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
@@ -1435,13 +1435,13 @@
       <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="46"/>
+      <c r="A9" s="51"/>
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="46"/>
+      <c r="A10" s="51"/>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
       <c r="E10" s="44"/>
@@ -1632,7 +1632,7 @@
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="51"/>
+      <c r="A36" s="50"/>
       <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
@@ -1640,7 +1640,7 @@
       <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="50"/>
+      <c r="A37" s="47"/>
       <c r="B37" s="21"/>
       <c r="C37" s="34"/>
       <c r="D37" s="35"/>
